--- a/data/output/template/template.xlsx
+++ b/data/output/template/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\PycharmProjects\ite_proctor_exam_telegram_bot\data\output\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096C6D51-4E52-4CAF-8FDE-B7D2202EBA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851B9F64-556C-4B14-9B75-58E84C122109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Экзамены" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>RISKC</t>
   </si>
   <si>
-    <t>SOA4C</t>
-  </si>
-  <si>
     <t>BASRMC</t>
   </si>
   <si>
@@ -122,6 +119,9 @@
   </si>
   <si>
     <t>01.03.2026</t>
+  </si>
+  <si>
+    <t>SOAC</t>
   </si>
 </sst>
 </file>
@@ -531,28 +531,28 @@
         <v>7</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -987,22 +987,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
@@ -1012,12 +1012,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
@@ -1037,22 +1037,22 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A19">
-    <sortCondition ref="A1:A19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A14">
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <conditionalFormatting sqref="A1 A9:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/data/output/template/template.xlsx
+++ b/data/output/template/template.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\PycharmProjects\ite_proctor_exam_telegram_bot\data\output\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.100\Administrative server\РАБОТА АДМИНИСТРАТОРА\ОРГАНИЗАЦИЯ IT ЭКЗАМЕНОВ\ЭКЗАМЕНЫ ЦИФРОВОЙ ПУТЬ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851B9F64-556C-4B14-9B75-58E84C122109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71823B9B-9331-4EFF-B7FF-2F534A5DE84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Экзамены" sheetId="1" r:id="rId1"/>
     <sheet name="exam_list" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Экзамены!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Экзамены!$C$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,36 +31,18 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
-    <t>Фамилия</t>
-  </si>
-  <si>
-    <t>Имя</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Экзамен</t>
   </si>
   <si>
-    <t>Дата</t>
-  </si>
-  <si>
     <t>Часы</t>
   </si>
   <si>
     <t>Минуты</t>
   </si>
   <si>
-    <t>Proctor</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
     <t>BAFC</t>
   </si>
   <si>
@@ -118,17 +100,38 @@
     <t>ITSMC</t>
   </si>
   <si>
-    <t>01.03.2026</t>
-  </si>
-  <si>
     <t>SOAC</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>20.01.2026</t>
+  </si>
+  <si>
+    <t>Фамилия рус</t>
+  </si>
+  <si>
+    <t>Имя рус</t>
+  </si>
+  <si>
+    <t>Фамилия англ</t>
+  </si>
+  <si>
+    <t>Имя анг</t>
+  </si>
+  <si>
+    <t>Дата экзамена</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00&quot;р.&quot;_-;\-* #,##0.00&quot;р.&quot;_-;_-* &quot;-&quot;??&quot;р.&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,31 +150,306 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="50"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="45"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="45"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="45"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="22"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="45"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="23"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="61"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="39"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="35"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -179,24 +457,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="38"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="38"/>
+      </top>
+      <bottom style="double">
+        <color indexed="38"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="8"/>
+      </left>
+      <right style="double">
+        <color indexed="8"/>
+      </right>
+      <top style="double">
+        <color indexed="8"/>
+      </top>
+      <bottom style="double">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="61" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="82">
+    <cellStyle name="20% — акцент1 2" xfId="16" xr:uid="{1E844D12-4850-45B2-801F-8B23C8E6D5B4}"/>
+    <cellStyle name="20% — акцент1 2 2" xfId="65" xr:uid="{F1C5E498-0634-4000-8D79-E0F3D2568AE4}"/>
+    <cellStyle name="20% — акцент2 2" xfId="17" xr:uid="{8FCE450E-1F73-4431-AA4B-E0AAEE220E75}"/>
+    <cellStyle name="20% — акцент2 2 2" xfId="66" xr:uid="{5FB0AA4A-90F2-425B-B8E9-E39B2E8D96E9}"/>
+    <cellStyle name="20% — акцент3 2" xfId="18" xr:uid="{970F022A-8860-451C-B47C-84732264F819}"/>
+    <cellStyle name="20% — акцент3 2 2" xfId="67" xr:uid="{15D48DB2-844E-4FBE-B9F1-6B48F2E22608}"/>
+    <cellStyle name="20% — акцент4" xfId="6" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% — акцент4 2" xfId="60" xr:uid="{1C35ABF6-D680-4910-9D47-25D668F9A33E}"/>
+    <cellStyle name="20% — акцент5 2" xfId="19" xr:uid="{7AB86D8D-8926-483E-B252-F777FC349D34}"/>
+    <cellStyle name="20% — акцент5 2 2" xfId="68" xr:uid="{E070B5BD-AE54-4EF9-B3E1-77B2D9F32CB0}"/>
+    <cellStyle name="20% — акцент6 2" xfId="20" xr:uid="{7241F9D7-43D1-4CF2-A977-52BE521A1A11}"/>
+    <cellStyle name="20% — акцент6 2 2" xfId="69" xr:uid="{D34D2B93-5486-4057-840D-2DCE9091B3FA}"/>
+    <cellStyle name="40% — акцент1 2" xfId="21" xr:uid="{A5C8BCDF-251A-4832-88E5-21897F8F0BC9}"/>
+    <cellStyle name="40% — акцент1 2 2" xfId="70" xr:uid="{5AA700C1-281D-4B36-B3E7-968CCA609488}"/>
+    <cellStyle name="40% — акцент2" xfId="4" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% — акцент2 2" xfId="59" xr:uid="{E8FFEED5-1DBA-4994-A435-9769769FD5C2}"/>
+    <cellStyle name="40% — акцент3 2" xfId="22" xr:uid="{BBB292AE-C277-4A18-9E2D-39A7EFCA39A0}"/>
+    <cellStyle name="40% — акцент3 2 2" xfId="71" xr:uid="{BEE8EAF7-F5D2-4C3E-8F8D-BF584BD001AE}"/>
+    <cellStyle name="40% — акцент4 2" xfId="23" xr:uid="{415DB589-728A-4FD9-B480-8987C027BFDE}"/>
+    <cellStyle name="40% — акцент4 2 2" xfId="72" xr:uid="{74E65902-F019-4D95-93BC-503DFCA7EEDE}"/>
+    <cellStyle name="40% — акцент5 2" xfId="24" xr:uid="{D3760155-9C4E-47E6-9A89-963993CA8508}"/>
+    <cellStyle name="40% — акцент5 2 2" xfId="73" xr:uid="{E7BB0E1D-91C2-460B-914C-AAE85C9531EB}"/>
+    <cellStyle name="40% — акцент6 2" xfId="25" xr:uid="{8F922D9E-342B-4F3A-B8F9-FA14F1DAFDB5}"/>
+    <cellStyle name="40% — акцент6 2 2" xfId="74" xr:uid="{572E6790-3392-4B8C-A986-049E517E9777}"/>
+    <cellStyle name="60% — акцент1 2" xfId="26" xr:uid="{BCBC8550-CC2C-4445-ADCB-FD826D619BBF}"/>
+    <cellStyle name="60% — акцент2 2" xfId="27" xr:uid="{A713374C-0DE8-40A6-A666-FDB050368DB5}"/>
+    <cellStyle name="60% — акцент3 2" xfId="28" xr:uid="{42E34028-7F86-48F7-9CA8-5B267174E33F}"/>
+    <cellStyle name="60% — акцент4 2" xfId="29" xr:uid="{70C8A04E-21EB-4A0F-9840-8DC8C9536DC3}"/>
+    <cellStyle name="60% — акцент5 2" xfId="30" xr:uid="{FEC74305-3FBD-47EB-9B1F-A9A02AEEEADE}"/>
+    <cellStyle name="60% — акцент6 2" xfId="31" xr:uid="{1EA0AAC1-300A-4AE9-8798-7653669A2BD2}"/>
+    <cellStyle name="Акцент1 2" xfId="32" xr:uid="{27D377CD-0C52-4515-978A-1ADA66D4977A}"/>
+    <cellStyle name="Акцент2 2" xfId="33" xr:uid="{89DC394D-48A8-4B75-8A2A-DC0D227EE40E}"/>
+    <cellStyle name="Акцент3 2" xfId="34" xr:uid="{73044CAE-574E-46B1-A22C-9AB2F56A3961}"/>
+    <cellStyle name="Акцент4" xfId="5" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Акцент5 2" xfId="35" xr:uid="{674726B9-6351-4EFA-A513-E8911F39C762}"/>
+    <cellStyle name="Акцент6 2" xfId="36" xr:uid="{ECC78E07-86FC-4FB3-909D-AC2D84ED8E38}"/>
+    <cellStyle name="Ввод  2" xfId="37" xr:uid="{D2CDAC57-BF42-4326-87F4-4BAD65965C23}"/>
+    <cellStyle name="Вывод 2" xfId="38" xr:uid="{60EBDB2B-F825-434D-B100-7C9E54106DE1}"/>
+    <cellStyle name="Вычисление 2" xfId="39" xr:uid="{FA6FEE81-B21E-4CF5-93A6-109DEDE3DDAD}"/>
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Гиперссылка 2" xfId="81" xr:uid="{86972A77-761D-40F8-BF27-C74351CED94C}"/>
+    <cellStyle name="Денежный 2" xfId="13" xr:uid="{EB148198-58BA-45A9-9ABA-5E12DB87862A}"/>
+    <cellStyle name="Денежный 2 2" xfId="63" xr:uid="{C3CD8E47-7342-4C60-835A-7E8394FFCB21}"/>
+    <cellStyle name="Заголовок 1 2" xfId="40" xr:uid="{AB9CB28E-F87E-46D6-BAF1-E8E2803E688B}"/>
+    <cellStyle name="Заголовок 2 2" xfId="41" xr:uid="{31E58A2B-2539-464D-A901-00354A2EF4A4}"/>
+    <cellStyle name="Заголовок 3 2" xfId="42" xr:uid="{20C71BCC-DA2A-4072-BF72-BD4263726524}"/>
+    <cellStyle name="Заголовок 4 2" xfId="43" xr:uid="{59EDEB8B-0A07-4598-B821-5439F39413E0}"/>
+    <cellStyle name="Итог 2" xfId="44" xr:uid="{836D1DE8-FABD-472D-BA45-F662D6D219B6}"/>
+    <cellStyle name="Контрольная ячейка 2" xfId="45" xr:uid="{F4008380-AADC-4701-B4C6-BAE7DD32FB3D}"/>
+    <cellStyle name="Название 2" xfId="46" xr:uid="{25C51EE5-021C-43C7-8263-313AEB2A79C7}"/>
+    <cellStyle name="Нейтральный 2" xfId="47" xr:uid="{AEAC39CC-B797-406E-A863-85746F5AEF0D}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 10" xfId="57" xr:uid="{5C896312-F1B2-4C94-8D01-67A836AAF840}"/>
+    <cellStyle name="Обычный 10 2" xfId="79" xr:uid="{10C82F0B-9F1B-442E-ADF2-18EA02AC2829}"/>
+    <cellStyle name="Обычный 11" xfId="61" xr:uid="{3D193B81-923C-467A-99FD-B826FB4CED3A}"/>
+    <cellStyle name="Обычный 12" xfId="58" xr:uid="{6AF94467-E87F-4978-9914-C5FFB847BA74}"/>
+    <cellStyle name="Обычный 13" xfId="80" xr:uid="{BE9D575E-D768-470C-B151-B272E44ACFCA}"/>
+    <cellStyle name="Обычный 14" xfId="7" xr:uid="{DFE41F05-1D7B-407F-8008-18CAFB19D299}"/>
+    <cellStyle name="Обычный 2" xfId="11" xr:uid="{13DC554C-7947-49E9-8306-A7B4C8A84EF8}"/>
+    <cellStyle name="Обычный 2 2" xfId="15" xr:uid="{EC2F1BB8-57A8-4BD2-B6C1-725FC441270F}"/>
+    <cellStyle name="Обычный 2 3" xfId="48" xr:uid="{73DBCDC3-7A41-4B80-A3E2-A8AF61039ACC}"/>
+    <cellStyle name="Обычный 2 4" xfId="56" xr:uid="{4DA6E508-988E-4A98-B3B6-1AC9234B0FF6}"/>
+    <cellStyle name="Обычный 2 4 2" xfId="78" xr:uid="{10193D09-51D5-4A15-9E05-7349297301A6}"/>
+    <cellStyle name="Обычный 3" xfId="8" xr:uid="{8C41F050-370E-41AD-905A-E960BBC93193}"/>
+    <cellStyle name="Обычный 4" xfId="12" xr:uid="{9C955282-8E13-41D3-B5B7-EDB6DB743EE0}"/>
+    <cellStyle name="Обычный 4 2" xfId="9" xr:uid="{F457D957-4712-4AA3-919F-295492836D35}"/>
+    <cellStyle name="Обычный 4 2 2" xfId="62" xr:uid="{3E013C3D-2C66-445A-8ABA-D8AF28FC086F}"/>
+    <cellStyle name="Обычный 5" xfId="14" xr:uid="{78D13E73-504C-4390-A961-43B6EF8D4D95}"/>
+    <cellStyle name="Обычный 5 2" xfId="64" xr:uid="{A5130FD6-686B-497F-828D-98455FB1C575}"/>
+    <cellStyle name="Обычный 6" xfId="53" xr:uid="{262E4957-6B3E-4774-BD2D-EED0CD51FD26}"/>
+    <cellStyle name="Обычный 6 2" xfId="75" xr:uid="{4431AFD6-A2F9-4FC4-8EE3-5CBD96548B9E}"/>
+    <cellStyle name="Обычный 7" xfId="10" xr:uid="{0EBC948B-B775-4982-9CBC-4BB85997F0B7}"/>
+    <cellStyle name="Обычный 8" xfId="54" xr:uid="{3A6E684F-165C-4683-A69D-4033272199B4}"/>
+    <cellStyle name="Обычный 8 2" xfId="76" xr:uid="{BD7D7308-4D8E-464E-85DF-B60A2BFC6FAD}"/>
+    <cellStyle name="Обычный 9" xfId="55" xr:uid="{3C4F4603-2D52-4983-B70B-6909A79782DB}"/>
+    <cellStyle name="Обычный 9 2" xfId="77" xr:uid="{DA935C0A-255F-447A-AEB1-73D034AE8B75}"/>
+    <cellStyle name="Плохой 2" xfId="49" xr:uid="{4F49D490-35F8-4739-AA8A-C40587222479}"/>
+    <cellStyle name="Пояснение 2" xfId="50" xr:uid="{A6A2B9CF-BB58-4DD0-8F3F-97E8E453D3A0}"/>
+    <cellStyle name="Примечание 2" xfId="51" xr:uid="{9932EF65-4399-43B6-97F6-8E86D7EA1928}"/>
+    <cellStyle name="Связанная ячейка" xfId="2" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Текст предупреждения" xfId="3" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Хороший 2" xfId="52" xr:uid="{A992E23D-C340-4E59-BDCC-6161DAFFA0B4}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -483,77 +1053,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12" style="1"/>
-    <col min="4" max="4" width="12" style="1"/>
-    <col min="5" max="5" width="16.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="12" style="1"/>
-    <col min="12" max="12" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="12" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3"/>
       <c r="I2">
         <v>10</v>
       </c>
@@ -567,407 +1144,397 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="1"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="1"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="1"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="1"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="1"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="1"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="1"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="2:11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-      <c r="H22" s="4"/>
+    <row r="3" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="D4" s="1"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="D6" s="1"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="D13" s="1"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G23"/>
+      <c r="B23"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G24"/>
+      <c r="B24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G25"/>
+      <c r="B25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G26"/>
+      <c r="B26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G27"/>
+      <c r="B27"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G28"/>
+      <c r="B28"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G29"/>
+      <c r="B29"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G30"/>
+      <c r="B30"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G31"/>
+      <c r="B31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G32"/>
+      <c r="B32"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
     </row>
-    <row r="33" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G33"/>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
     </row>
-    <row r="34" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G34"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
     </row>
-    <row r="35" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G35"/>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
     </row>
-    <row r="36" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G36"/>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
     </row>
-    <row r="37" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G37"/>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37"/>
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
     </row>
-    <row r="38" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G38"/>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38"/>
       <c r="I38"/>
       <c r="J38"/>
       <c r="K38"/>
     </row>
-    <row r="39" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G39"/>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39"/>
       <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
     </row>
-    <row r="40" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G40"/>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40"/>
       <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
     </row>
-    <row r="41" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G41"/>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41"/>
       <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
     </row>
-    <row r="42" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G42"/>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42"/>
       <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
     </row>
-    <row r="43" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G43"/>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43"/>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
     </row>
-    <row r="44" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G44"/>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44"/>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
     </row>
-    <row r="45" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G45"/>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45"/>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
     </row>
-    <row r="46" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G46"/>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46"/>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
     </row>
-    <row r="47" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G47"/>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47"/>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
     </row>
-    <row r="48" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G48"/>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48"/>
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
     </row>
-    <row r="49" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G49"/>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49"/>
       <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
     </row>
-    <row r="50" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G50"/>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50"/>
       <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
     </row>
-    <row r="51" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G51"/>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51"/>
       <c r="I51"/>
       <c r="J51"/>
       <c r="K51"/>
     </row>
-    <row r="52" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G52"/>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52"/>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
     </row>
-    <row r="53" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G53"/>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53"/>
       <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
     </row>
-    <row r="54" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G54"/>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54"/>
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54"/>
     </row>
-    <row r="55" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G55"/>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55"/>
       <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
     </row>
-    <row r="56" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G56"/>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56"/>
       <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
     </row>
-    <row r="57" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G57"/>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
     </row>
-    <row r="58" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G58"/>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
     </row>
-    <row r="59" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G59"/>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
     </row>
-    <row r="60" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G60"/>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60"/>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
     </row>
-    <row r="61" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G61"/>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61"/>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
     </row>
-    <row r="62" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G62"/>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62"/>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
     </row>
-    <row r="63" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G63"/>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63"/>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
     </row>
-    <row r="64" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G64"/>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64"/>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
     </row>
-    <row r="65" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-    </row>
-    <row r="66" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-    </row>
-    <row r="67" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-    </row>
-    <row r="68" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-    </row>
-    <row r="69" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-    </row>
-    <row r="70" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-    </row>
-    <row r="71" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71"/>
-    </row>
-    <row r="72" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-    </row>
-    <row r="73" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B9:B14">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{6D84B703-F22B-4C28-A457-80194876DCD8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>exam_list!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G110</xm:sqref>
+          <xm:sqref>B2:B101</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -982,72 +1549,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
